--- a/servers/maze_main_server/conf.d/data/maze_kongfu_hit_time_v8【迷宫-武力比-怪物受击死亡动作档位】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_kongfu_hit_time_v8【迷宫-武力比-怪物受击死亡动作档位】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EABFF67-81C6-4085-B95E-3CBA52751AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E853A7BF-374F-44A2-8217-64F746E42BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{49B82B9C-8AEC-4622-8430-8B97FEAB0D61}"/>
   </bookViews>
@@ -104,11 +104,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>LIST_C</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>900300,900301,900302,900303,900304,900305,900306,900307,900308,900309,900310,900311</t>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -564,7 +564,7 @@
         <v>2</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
@@ -679,7 +679,7 @@
         <v>900007</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
